--- a/survey_templates/046_tournament_venue_experience_survey--survey_templates.xlsx
+++ b/survey_templates/046_tournament_venue_experience_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Bad'}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'food_and_beverage_services'}</t>
+          <t>food_and_beverage_services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Food and beverage services'}</t>
+          <t>Food and beverage services</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'restrooms_and_facilities'}</t>
+          <t>restrooms_and_facilities</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Restrooms and facilities'}</t>
+          <t>Restrooms and facilities</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'event_staff_and_volunteers'}</t>
+          <t>event_staff_and_volunteers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Event staff and volunteers'}</t>
+          <t>Event staff and volunteers</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'parking_and_transportation'}</t>
+          <t>parking_and_transportation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Parking and transportation'}</t>
+          <t>Parking and transportation</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'overall_experience'}</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Overall experience'}</t>
+          <t>Overall experience</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Bad'}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
